--- a/Data/UEFA Stats 2019_with_IDs.xlsx
+++ b/Data/UEFA Stats 2019_with_IDs.xlsx
@@ -2657,7 +2657,7 @@
         <v>32.2</v>
       </c>
       <c r="J3">
-        <v>288230</v>
+        <v>200512</v>
       </c>
     </row>
     <row r="4" spans="1:10">
